--- a/docs/formato-importacion-full.xlsx
+++ b/docs/formato-importacion-full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\gestor-de-tareas\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{937D4E11-9701-434F-8AFE-93EC7CD5C27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CAD4BA8-843E-4217-8064-D3A9D84AE738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{927B6FF0-DB27-4537-AF19-7DABD98CF81C}"/>
   </bookViews>
@@ -28,9 +28,6 @@
     <t>kit</t>
   </si>
   <si>
-    <t>kit_unidades</t>
-  </si>
-  <si>
     <t>producto_codigo</t>
   </si>
   <si>
@@ -128,6 +125,9 @@
   </si>
   <si>
     <t>Land Rover Defender 110</t>
+  </si>
+  <si>
+    <t>kit_producto_unidades</t>
   </si>
 </sst>
 </file>
@@ -995,7 +995,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="51.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1014,31 +1014,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1046,25 +1046,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I2">
         <v>1200.3599999999999</v>
@@ -1073,30 +1073,33 @@
         <v>1000</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I3">
         <v>1500.95</v>
@@ -1105,30 +1108,33 @@
         <v>1000</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
         <v>13</v>
       </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I4">
         <v>350.25</v>
@@ -1137,30 +1143,33 @@
         <v>1000</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
         <v>13</v>
       </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I5">
         <v>450.36</v>
@@ -1169,30 +1178,33 @@
         <v>1000</v>
       </c>
       <c r="K5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>13</v>
       </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I6">
         <v>760.45</v>
@@ -1201,30 +1213,33 @@
         <v>1000</v>
       </c>
       <c r="K6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2</v>
+      </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" t="s">
         <v>15</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" t="s">
-        <v>16</v>
       </c>
       <c r="I7">
         <v>150.24</v>
@@ -1233,30 +1248,33 @@
         <v>1000</v>
       </c>
       <c r="K7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2</v>
+      </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" t="s">
         <v>34</v>
       </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I8">
         <v>675.89</v>
@@ -1265,30 +1283,33 @@
         <v>1000</v>
       </c>
       <c r="K8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2</v>
+      </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" t="s">
         <v>34</v>
       </c>
-      <c r="G9" t="s">
-        <v>35</v>
-      </c>
       <c r="H9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I9">
         <v>700.25</v>
@@ -1297,7 +1318,7 @@
         <v>1000</v>
       </c>
       <c r="K9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/docs/formato-importacion-full.xlsx
+++ b/docs/formato-importacion-full.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\gestor-de-tareas\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CAD4BA8-843E-4217-8064-D3A9D84AE738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{927B6FF0-DB27-4537-AF19-7DABD98CF81C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="formato-importacion" sheetId="1" r:id="rId1"/>
@@ -20,10 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="36">
-  <si>
-    <t>id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
   <si>
     <t>kit</t>
   </si>
@@ -133,8 +129,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -990,31 +986,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E9BB801-10B4-470B-B170-FEED8F8A7416}">
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="25.28515625" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.7109375" customWidth="1"/>
-    <col min="8" max="8" width="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" customWidth="1"/>
-    <col min="11" max="11" width="30.5703125" customWidth="1"/>
+    <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.75" customWidth="1"/>
+    <col min="7" max="7" width="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" customWidth="1"/>
+    <col min="9" max="9" width="17.75" customWidth="1"/>
+    <col min="10" max="10" width="30.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1037,288 +1033,261 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
       <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
       </c>
       <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2">
+        <v>1200.3599999999999</v>
+      </c>
+      <c r="I2">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2">
-        <v>1200.3599999999999</v>
-      </c>
-      <c r="J2">
-        <v>1000</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3">
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
         <v>4</v>
       </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="H3">
+        <v>1500.95</v>
       </c>
       <c r="I3">
-        <v>1500.95</v>
-      </c>
-      <c r="J3">
         <v>1000</v>
       </c>
-      <c r="K3" t="s">
-        <v>25</v>
+      <c r="J3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4">
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
         <v>2</v>
       </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="H4">
+        <v>350.25</v>
       </c>
       <c r="I4">
-        <v>350.25</v>
-      </c>
-      <c r="J4">
         <v>1000</v>
       </c>
-      <c r="K4" t="s">
-        <v>26</v>
+      <c r="J4" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
         <v>3</v>
       </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>450.36</v>
       </c>
       <c r="I5">
-        <v>450.36</v>
-      </c>
-      <c r="J5">
         <v>1000</v>
       </c>
-      <c r="K5" t="s">
-        <v>27</v>
+      <c r="J5" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>760.45</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6">
-        <v>760.45</v>
-      </c>
-      <c r="J6">
-        <v>1000</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="D7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="E7" t="s">
         <v>32</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
       </c>
       <c r="F7" t="s">
         <v>33</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="H7">
+        <v>150.24</v>
       </c>
       <c r="I7">
-        <v>150.24</v>
-      </c>
-      <c r="J7">
         <v>1000</v>
       </c>
-      <c r="K7" t="s">
-        <v>11</v>
+      <c r="J7" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
         <v>32</v>
-      </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
       </c>
       <c r="F8" t="s">
         <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="H8">
+        <v>675.89</v>
       </c>
       <c r="I8">
-        <v>675.89</v>
-      </c>
-      <c r="J8">
         <v>1000</v>
       </c>
-      <c r="K8" t="s">
-        <v>17</v>
+      <c r="J8" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9">
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9">
         <v>2</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
         <v>32</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
       </c>
       <c r="F9" t="s">
         <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="H9">
+        <v>700.25</v>
       </c>
       <c r="I9">
-        <v>700.25</v>
-      </c>
-      <c r="J9">
         <v>1000</v>
       </c>
-      <c r="K9" t="s">
-        <v>18</v>
+      <c r="J9" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/docs/formato-importacion-full.xlsx
+++ b/docs/formato-importacion-full.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\gestor-de-tareas\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF65F5A2-4612-4F07-85E2-4E5841E98BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="formato-importacion" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="44">
   <si>
     <t>kit</t>
   </si>
@@ -96,15 +97,9 @@
     <t>6524871KH</t>
   </si>
   <si>
-    <t>9658741BR</t>
-  </si>
-  <si>
     <t>9632547FD</t>
   </si>
   <si>
-    <t>6321458PW</t>
-  </si>
-  <si>
     <t>Topes de suspensión ajustables para recorridos largos</t>
   </si>
   <si>
@@ -124,13 +119,46 @@
   </si>
   <si>
     <t>kit_producto_unidades</t>
+  </si>
+  <si>
+    <t>Instalación de tienda en Land Rover</t>
+  </si>
+  <si>
+    <t>8315645HM</t>
+  </si>
+  <si>
+    <t>Tienda ensamblable en vehículos 4x4</t>
+  </si>
+  <si>
+    <t>Land Rover Defender 250</t>
+  </si>
+  <si>
+    <t>Camping para vehículos</t>
+  </si>
+  <si>
+    <t>8315646HM</t>
+  </si>
+  <si>
+    <t>8315647HM</t>
+  </si>
+  <si>
+    <t>8315648HM</t>
+  </si>
+  <si>
+    <t>Barras estabilizadoras laterales</t>
+  </si>
+  <si>
+    <t>Pernos para ensamble impermeable</t>
+  </si>
+  <si>
+    <t>Techo lateral para protección del sol</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -986,28 +1014,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.75" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.875" customWidth="1"/>
-    <col min="9" max="9" width="17.75" customWidth="1"/>
-    <col min="10" max="10" width="30.625" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="30.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -1034,12 +1062,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -1062,11 +1090,8 @@
       <c r="I2">
         <v>1000</v>
       </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1094,11 +1119,8 @@
       <c r="I3">
         <v>1000</v>
       </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1126,11 +1148,8 @@
       <c r="I4">
         <v>1000</v>
       </c>
-      <c r="J4" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1158,11 +1177,8 @@
       <c r="I5">
         <v>1000</v>
       </c>
-      <c r="J5" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1190,13 +1206,10 @@
       <c r="I6">
         <v>1000</v>
       </c>
-      <c r="J6" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -1205,13 +1218,13 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
         <v>14</v>
@@ -1226,9 +1239,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -1237,13 +1250,13 @@
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
         <v>14</v>
@@ -1258,24 +1271,24 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
         <v>30</v>
       </c>
-      <c r="E9" t="s">
-        <v>32</v>
-      </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
         <v>14</v>
@@ -1288,6 +1301,131 @@
       </c>
       <c r="J9" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10">
+        <v>1300.6500000000001</v>
+      </c>
+      <c r="I10">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11">
+        <v>200.15</v>
+      </c>
+      <c r="I11">
+        <v>500</v>
+      </c>
+      <c r="J11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12">
+        <v>25.36</v>
+      </c>
+      <c r="I12">
+        <v>500</v>
+      </c>
+      <c r="J12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13">
+        <v>65.34</v>
+      </c>
+      <c r="I13">
+        <v>500</v>
+      </c>
+      <c r="J13" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/docs/formato-importacion-full.xlsx
+++ b/docs/formato-importacion-full.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\gestor-de-tareas\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF65F5A2-4612-4F07-85E2-4E5841E98BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="formato-importacion" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="44">
   <si>
     <t>kit</t>
   </si>
@@ -157,8 +156,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1014,23 +1013,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="30.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1062,7 +1061,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1090,8 +1089,11 @@
       <c r="I2">
         <v>1000</v>
       </c>
+      <c r="J2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1119,8 +1121,11 @@
       <c r="I3">
         <v>1000</v>
       </c>
+      <c r="J3" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1148,8 +1153,11 @@
       <c r="I4">
         <v>1000</v>
       </c>
+      <c r="J4" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1177,8 +1185,11 @@
       <c r="I5">
         <v>1000</v>
       </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1206,8 +1217,11 @@
       <c r="I6">
         <v>1000</v>
       </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1239,7 +1253,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1271,7 +1285,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1303,7 +1317,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -1332,7 +1346,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1364,7 +1378,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1396,7 +1410,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>33</v>
       </c>

--- a/docs/formato-importacion-full.xlsx
+++ b/docs/formato-importacion-full.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\gestor-de-tareas\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98ACA347-D2EF-4975-84FE-FBDABA56F05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="formato-importacion" sheetId="1" r:id="rId1"/>
@@ -156,8 +157,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1013,23 +1014,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1061,7 +1062,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1093,7 +1094,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1125,7 +1126,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1157,7 +1158,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1189,7 +1190,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1221,7 +1222,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1253,7 +1254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1285,7 +1286,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1317,7 +1318,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -1346,7 +1347,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1378,7 +1379,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1410,7 +1411,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>33</v>
       </c>
